--- a/data/gravel/Obed Boundary 2025.xlsx
+++ b/data/gravel/Obed Boundary 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0017B16-79D1-3C42-B410-9EA7F687E799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503036D3-7B8E-AC4A-8AED-FDC9EE2D892B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1820" yWindow="1420" windowWidth="26840" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1820" yWindow="500" windowWidth="26840" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -321,21 +321,6 @@
   </si>
   <si>
     <t>Top Tube Length</t>
-  </si>
-  <si>
-    <t>51.8cm</t>
-  </si>
-  <si>
-    <t>52.7cm</t>
-  </si>
-  <si>
-    <t>54.4cm</t>
-  </si>
-  <si>
-    <t>56cm</t>
-  </si>
-  <si>
-    <t>58cm</t>
   </si>
   <si>
     <t>Fork axle to crown</t>
@@ -729,7 +714,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -753,7 +738,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -761,7 +746,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="21">
@@ -792,34 +777,39 @@
         <v>95</v>
       </c>
       <c r="C9">
+        <f>H9*10</f>
+        <v>520</v>
+      </c>
+      <c r="D9">
+        <f t="shared" ref="D9:G9" si="0">I9*10</f>
+        <v>535</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>550</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>565</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>580</v>
+      </c>
+      <c r="H9">
         <v>52</v>
       </c>
-      <c r="D9">
+      <c r="I9">
         <v>53.5</v>
       </c>
-      <c r="E9">
+      <c r="J9">
         <v>55</v>
       </c>
-      <c r="F9">
+      <c r="K9">
         <v>56.5</v>
       </c>
-      <c r="G9">
+      <c r="L9">
         <v>58</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="K9" t="s">
-        <v>99</v>
-      </c>
-      <c r="L9" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="21">
@@ -998,19 +988,19 @@
         <v>759</v>
       </c>
       <c r="D17">
-        <f t="shared" ref="D17:G17" si="0">I17*10</f>
+        <f t="shared" ref="D17:G17" si="1">I17*10</f>
         <v>786</v>
       </c>
       <c r="E17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>803</v>
       </c>
       <c r="F17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>823</v>
       </c>
       <c r="G17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>843</v>
       </c>
       <c r="H17">
@@ -1034,7 +1024,7 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C18">
         <v>395</v>
@@ -1057,7 +1047,7 @@
         <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C19">
         <v>50</v>
@@ -1338,7 +1328,7 @@
         <v>33</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -1403,7 +1393,7 @@
         <v>43</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:2">

--- a/data/gravel/Obed Boundary 2025.xlsx
+++ b/data/gravel/Obed Boundary 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{503036D3-7B8E-AC4A-8AED-FDC9EE2D892B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9FA013-0438-2649-B359-E3F0D4027FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1820" yWindow="500" windowWidth="26840" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>https://obedbikes.com/cdn/shop/files/OB-GVR-Colombia-Austin-AM-05.jpg?v=1752551352&amp;width=1800</t>
   </si>
 </sst>
 </file>
@@ -741,6 +744,11 @@
         <v>100</v>
       </c>
     </row>
+    <row r="6" spans="1:12">
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+    </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Obed Boundary 2025.xlsx
+++ b/data/gravel/Obed Boundary 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9FA013-0438-2649-B359-E3F0D4027FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753F5F05-36F7-7849-93AB-3BEFE0A0D808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1820" yWindow="500" windowWidth="26840" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5940" yWindow="500" windowWidth="26840" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,12 @@
   </si>
   <si>
     <t>https://obedbikes.com/cdn/shop/files/OB-GVR-Colombia-Austin-AM-05.jpg?v=1752551352&amp;width=1800</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Chattanooga, Tennessee, USA</t>
   </si>
 </sst>
 </file>
@@ -697,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1572,6 +1578,14 @@
         <v>93</v>
       </c>
     </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>104</v>
+      </c>
+      <c r="B73" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Obed Boundary 2025.xlsx
+++ b/data/gravel/Obed Boundary 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{753F5F05-36F7-7849-93AB-3BEFE0A0D808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1A9986-CB1D-9048-902F-2291D91CFAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5940" yWindow="500" windowWidth="26840" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10700" yWindow="-22980" windowWidth="26840" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/gravel/Obed Boundary 2025.xlsx
+++ b/data/gravel/Obed Boundary 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB1A9986-CB1D-9048-902F-2291D91CFAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A09E2FC-0E31-C544-A214-1E937CF85DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10700" yWindow="-22980" windowWidth="26840" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,24 @@
   </si>
   <si>
     <t>Chattanooga, Tennessee, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -703,7 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1404,185 +1422,215 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>46</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="1">
-        <v>52</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>49</v>
-      </c>
-      <c r="B55" s="1">
-        <v>180</v>
+        <v>43</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>50</v>
-      </c>
-      <c r="B56" s="1">
-        <v>160</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B57">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="1" t="s">
-        <v>52</v>
+      <c r="A58" t="s">
+        <v>46</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>86</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B60" s="1">
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B61" s="1">
+        <v>180</v>
+      </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B62" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
+      <c r="A64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="1">
-        <v>3</v>
+        <v>53</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>60</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>68</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B69">
-        <v>1899</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>64</v>
-      </c>
-      <c r="B70">
-        <v>3299</v>
+        <v>58</v>
+      </c>
+      <c r="B70" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>59</v>
+      </c>
+      <c r="B71" s="1">
+        <v>3</v>
+      </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
+        <v>61</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76">
+        <v>3299</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>65</v>
+      </c>
+      <c r="B77" s="1"/>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>66</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
         <v>104</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>105</v>
       </c>
     </row>
